--- a/data/trans_dic/P16A09-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P16A09-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas</t>
+          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,32 +717,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,73</t>
+          <t>1,16; 4,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 5,04</t>
+          <t>1,2; 4,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,12</t>
+          <t>0,17; 1,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,86</t>
+          <t>0,33; 1,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,79; 6,31</t>
+          <t>1,65; 6,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,52</t>
+          <t>0,35; 3,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -752,27 +752,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,82; 4,44</t>
+          <t>1,8; 4,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 4,35</t>
+          <t>1,75; 4,32</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,6</t>
+          <t>1,26; 3,81</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,83</t>
+          <t>0,37; 1,73</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 2,68</t>
+          <t>1,22; 2,76</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,7</t>
+          <t>0,47; 2,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,71</t>
+          <t>0,77; 3,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,7</t>
+          <t>0,55; 2,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,77</t>
+          <t>0,98; 4,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,76</t>
+          <t>1,21; 4,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,12</t>
+          <t>0,31; 2,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,67; 5,89</t>
+          <t>2,68; 5,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,13</t>
+          <t>0,89; 3,06</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,24</t>
+          <t>1,11; 3,28</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,46</t>
+          <t>0,15; 1,41</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,78; 3,65</t>
+          <t>1,76; 3,61</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,4</t>
+          <t>1,53; 4,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,84</t>
+          <t>1,06; 4,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 2,12</t>
+          <t>0,22; 1,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,11</t>
+          <t>0,37; 3,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,23; 11,77</t>
+          <t>3,33; 12,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,99; 7,34</t>
+          <t>1,97; 7,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 8,69</t>
+          <t>1,27; 8,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,03; 14,05</t>
+          <t>5,23; 13,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,43; 5,25</t>
+          <t>2,42; 5,47</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,78; 4,41</t>
+          <t>1,68; 4,25</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,12</t>
+          <t>0,76; 2,86</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 4,73</t>
+          <t>1,13; 4,61</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,29; 5,46</t>
+          <t>3,33; 5,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,37</t>
+          <t>1,53; 3,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,1</t>
+          <t>1,32; 3,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 3,63</t>
+          <t>1,82; 3,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,66; 5,58</t>
+          <t>2,79; 5,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,4</t>
+          <t>1,88; 4,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,12</t>
+          <t>0,95; 2,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,52</t>
+          <t>1,19; 3,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,44; 5,15</t>
+          <t>3,39; 5,21</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,98; 3,45</t>
+          <t>1,93; 3,37</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 2,76</t>
+          <t>1,4; 2,77</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,26</t>
+          <t>1,79; 3,32</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,5; 4,77</t>
+          <t>1,51; 4,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,27; 4,0</t>
+          <t>1,29; 4,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,57</t>
+          <t>1,27; 3,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,72</t>
+          <t>1,43; 3,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,5; 7,21</t>
+          <t>3,54; 7,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,29; 9,01</t>
+          <t>5,27; 8,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,2; 7,79</t>
+          <t>4,23; 7,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,09; 9,35</t>
+          <t>5,14; 9,47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,98; 5,74</t>
+          <t>3,14; 5,81</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,86; 6,34</t>
+          <t>3,98; 6,47</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,18; 5,33</t>
+          <t>3,22; 5,4</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,11; 6,82</t>
+          <t>4,14; 6,86</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,5</t>
+          <t>0,0; 1,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,72</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,44; 8,37</t>
+          <t>5,29; 8,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,92; 11,62</t>
+          <t>8,04; 11,78</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,17; 7,2</t>
+          <t>4,27; 7,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,19; 8,83</t>
+          <t>6,21; 9,1</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,39; 6,65</t>
+          <t>4,33; 6,55</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6,48; 9,56</t>
+          <t>6,61; 9,61</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,32; 5,56</t>
+          <t>3,26; 5,58</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,54; 6,84</t>
+          <t>4,58; 6,9</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,38; 3,54</t>
+          <t>2,37; 3,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,67</t>
+          <t>1,59; 2,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,98; 1,76</t>
+          <t>1,0; 1,76</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,22</t>
+          <t>1,3; 2,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,38; 5,88</t>
+          <t>4,41; 5,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,02; 6,64</t>
+          <t>5,04; 6,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,08; 4,47</t>
+          <t>3,09; 4,4</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,15; 5,79</t>
+          <t>4,05; 5,82</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,53; 4,51</t>
+          <t>3,55; 4,52</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,51; 4,52</t>
+          <t>3,51; 4,48</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,19; 3,0</t>
+          <t>2,19; 3,01</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,93; 3,96</t>
+          <t>2,9; 3,9</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas</t>
+          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5516; 22414</t>
+          <t>5512; 20528</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5234; 22041</t>
+          <t>5240; 21445</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>732; 9089</t>
+          <t>733; 7954</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1857; 9389</t>
+          <t>1661; 9502</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5478; 19342</t>
+          <t>5069; 19797</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1294; 11057</t>
+          <t>1101; 10441</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1100; 10472</t>
+          <t>1103; 10489</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8162; 19880</t>
+          <t>8040; 19268</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13870; 33943</t>
+          <t>13679; 33692</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8375; 27066</t>
+          <t>9473; 28605</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3088; 14199</t>
+          <t>2892; 13404</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11443; 25513</t>
+          <t>11589; 26258</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1739; 9917</t>
+          <t>1720; 9861</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3089; 15457</t>
+          <t>3213; 14574</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2040</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2464; 12205</t>
+          <t>2496; 12568</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3562; 17738</t>
+          <t>3642; 16971</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3981; 15973</t>
+          <t>4060; 16396</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1129; 11615</t>
+          <t>1148; 10647</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10182; 22463</t>
+          <t>10242; 22329</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6913; 23107</t>
+          <t>6610; 22610</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9156; 24395</t>
+          <t>8337; 24685</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1149; 10937</t>
+          <t>1143; 10569</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14879; 30426</t>
+          <t>14708; 30116</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8037; 23890</t>
+          <t>8299; 23781</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7235; 24073</t>
+          <t>6665; 25581</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>939; 11058</t>
+          <t>1138; 10140</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2916; 20774</t>
+          <t>2467; 20731</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5417; 19746</t>
+          <t>5594; 20476</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5136; 18935</t>
+          <t>5089; 20542</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2075; 14429</t>
+          <t>2105; 13561</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8394; 23450</t>
+          <t>8733; 23027</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17265; 37307</t>
+          <t>17197; 38826</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15745; 38982</t>
+          <t>14894; 37562</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5352; 21450</t>
+          <t>5224; 19704</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10250; 39531</t>
+          <t>9448; 38526</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>40694; 67623</t>
+          <t>41183; 68589</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17191; 38980</t>
+          <t>17751; 38791</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15430; 35606</t>
+          <t>15152; 36664</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18707; 37548</t>
+          <t>18823; 37596</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19000; 39840</t>
+          <t>19928; 40759</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14555; 33722</t>
+          <t>14399; 32709</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8794; 25783</t>
+          <t>7847; 24661</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10347; 34418</t>
+          <t>11633; 36446</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>67130; 100496</t>
+          <t>66253; 101683</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>38034; 66467</t>
+          <t>37223; 64885</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28846; 54489</t>
+          <t>27624; 54670</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>36128; 65524</t>
+          <t>35969; 66837</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5256; 16680</t>
+          <t>5278; 16990</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6501; 20411</t>
+          <t>6575; 21733</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8505; 22185</t>
+          <t>7895; 22415</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6813; 17613</t>
+          <t>6770; 17933</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>19929; 40994</t>
+          <t>20154; 42195</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>40058; 68203</t>
+          <t>39911; 67497</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31036; 57517</t>
+          <t>31260; 58207</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>42736; 78426</t>
+          <t>43130; 79450</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>27407; 52670</t>
+          <t>28821; 53357</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>48882; 80408</t>
+          <t>50457; 82011</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>43189; 72483</t>
+          <t>43726; 73362</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>53962; 89503</t>
+          <t>54316; 90096</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4476</t>
+          <t>0; 5621</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1925</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 2019</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 4080</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>67937; 104530</t>
+          <t>66099; 102211</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>87523; 128474</t>
+          <t>88847; 130161</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>45112; 77922</t>
+          <t>46159; 78478</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>47086; 67150</t>
+          <t>47171; 69188</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>67911; 102860</t>
+          <t>67026; 101294</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>88829; 131025</t>
+          <t>90579; 131701</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>45502; 76136</t>
+          <t>44638; 76439</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>45402; 68419</t>
+          <t>45862; 69031</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>77902; 115691</t>
+          <t>77395; 117165</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>54881; 91214</t>
+          <t>54149; 91263</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>33092; 59500</t>
+          <t>33695; 59462</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>43949; 74937</t>
+          <t>43696; 73711</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>148105; 198511</t>
+          <t>149057; 198522</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>177579; 234936</t>
+          <t>178404; 233981</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>108733; 157934</t>
+          <t>109126; 155476</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>148099; 207016</t>
+          <t>144772; 207958</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>234446; 299592</t>
+          <t>235805; 300256</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>244115; 314381</t>
+          <t>244133; 311081</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>151249; 207597</t>
+          <t>151754; 208171</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>203662; 275006</t>
+          <t>201253; 270720</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A09-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P16A09-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,33</t>
+          <t>1,26; 4,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,91</t>
+          <t>1,24; 4,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,85</t>
+          <t>0,17; 1,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,88</t>
+          <t>0,37; 2,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,65; 6,46</t>
+          <t>1,71; 6,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,32</t>
+          <t>0,36; 3,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,02</t>
+          <t>0,32; 3,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,31</t>
+          <t>1,94; 4,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,75; 4,32</t>
+          <t>1,73; 4,31</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,81</t>
+          <t>1,13; 3,47</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,73</t>
+          <t>0,4; 1,87</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,76</t>
+          <t>1,24; 2,74</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,69</t>
+          <t>0,48; 2,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,49</t>
+          <t>0,73; 3,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,47 +872,47 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,78</t>
+          <t>0,59; 2,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,56</t>
+          <t>0,97; 4,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,89</t>
+          <t>1,2; 4,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,86</t>
+          <t>0,28; 2,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,68; 5,85</t>
+          <t>2,57; 5,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,06</t>
+          <t>0,99; 3,24</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,28</t>
+          <t>1,1; 3,1</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,41</t>
+          <t>0,14; 1,41</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,76; 3,61</t>
+          <t>1,81; 3,59</t>
         </is>
       </c>
     </row>
@@ -944,47 +944,47 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>6,79%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4,02%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3,75%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>8,35%</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>3,7%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
           <t>1,53%</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>6,79%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4,02%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,75%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>8,31%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,38</t>
+          <t>1,65; 4,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,08</t>
+          <t>1,17; 3,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,94</t>
+          <t>0,18; 1,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,1</t>
+          <t>1,21; 4,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,33; 12,2</t>
+          <t>3,25; 11,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 7,96</t>
+          <t>1,97; 7,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,27; 8,16</t>
+          <t>1,29; 8,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,23; 13,8</t>
+          <t>5,16; 13,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,42; 5,47</t>
+          <t>2,38; 5,5</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,25</t>
+          <t>1,75; 4,21</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,86</t>
+          <t>0,75; 2,9</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,61</t>
+          <t>2,75; 5,97</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,33; 5,54</t>
+          <t>3,35; 5,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,35</t>
+          <t>1,55; 3,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,19</t>
+          <t>1,37; 3,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,82; 3,64</t>
+          <t>1,78; 3,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,79; 5,71</t>
+          <t>2,63; 5,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,27</t>
+          <t>1,89; 4,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,99</t>
+          <t>1,08; 2,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,73</t>
+          <t>2,52; 4,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,39; 5,21</t>
+          <t>3,32; 5,11</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,93; 3,37</t>
+          <t>1,93; 3,34</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,77</t>
+          <t>1,34; 2,66</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,79; 3,32</t>
+          <t>2,35; 3,64</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,86</t>
+          <t>1,39; 4,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,26</t>
+          <t>1,26; 4,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,27; 3,61</t>
+          <t>1,28; 3,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,43; 3,79</t>
+          <t>1,26; 3,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,54; 7,42</t>
+          <t>3,32; 7,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,27; 8,91</t>
+          <t>5,26; 8,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,23; 7,88</t>
+          <t>4,22; 7,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,14; 9,47</t>
+          <t>5,88; 8,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,14; 5,81</t>
+          <t>3,16; 5,79</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,98; 6,47</t>
+          <t>3,88; 6,38</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,22; 5,4</t>
+          <t>3,24; 5,5</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,14; 6,86</t>
+          <t>4,26; 6,1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,88</t>
+          <t>0,0; 1,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1437,42 +1437,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,29; 8,19</t>
+          <t>5,34; 8,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,04; 11,78</t>
+          <t>7,99; 11,78</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,27; 7,25</t>
+          <t>4,21; 7,13</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,21; 9,1</t>
+          <t>6,07; 9,12</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,33; 6,55</t>
+          <t>4,27; 6,57</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6,61; 9,61</t>
+          <t>6,46; 9,51</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,26; 5,58</t>
+          <t>3,3; 5,62</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,58; 6,9</t>
+          <t>4,85; 7,07</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,37; 3,58</t>
+          <t>2,4; 3,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,59; 2,67</t>
+          <t>1,61; 2,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,76</t>
+          <t>0,99; 1,76</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,18</t>
+          <t>1,47; 2,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,41; 5,88</t>
+          <t>4,38; 5,91</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,04; 6,62</t>
+          <t>5,04; 6,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,09; 4,4</t>
+          <t>3,12; 4,45</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,05; 5,82</t>
+          <t>4,89; 6,09</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,55; 4,52</t>
+          <t>3,57; 4,57</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,51; 4,48</t>
+          <t>3,51; 4,49</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,19; 3,01</t>
+          <t>2,2; 3,0</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,9; 3,9</t>
+          <t>3,34; 4,15</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4522</t>
+          <t>4948</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12912</t>
+          <t>14553</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17433</t>
+          <t>19501</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5512; 20528</t>
+          <t>5981; 20620</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5240; 21445</t>
+          <t>5424; 21115</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>733; 7954</t>
+          <t>735; 8149</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1661; 9502</t>
+          <t>2062; 11946</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5069; 19797</t>
+          <t>5237; 19539</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1101; 10441</t>
+          <t>1118; 10569</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1103; 10489</t>
+          <t>1101; 10445</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8040; 19268</t>
+          <t>9489; 23957</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13679; 33692</t>
+          <t>13517; 33656</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9473; 28605</t>
+          <t>8489; 26084</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2892; 13404</t>
+          <t>3115; 14502</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11589; 26258</t>
+          <t>12878; 28505</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6049</t>
+          <t>6439</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15401</t>
+          <t>16721</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21450</t>
+          <t>23160</t>
         </is>
       </c>
     </row>
@@ -2135,12 +2135,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1720; 9861</t>
+          <t>1753; 9972</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3213; 14574</t>
+          <t>3065; 13693</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2150,47 +2150,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2496; 12568</t>
+          <t>2858; 14004</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3642; 16971</t>
+          <t>3589; 17200</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4060; 16396</t>
+          <t>4032; 15303</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1148; 10647</t>
+          <t>1027; 9871</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10242; 22329</t>
+          <t>10864; 23693</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6610; 22610</t>
+          <t>7317; 23912</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8337; 24685</t>
+          <t>8294; 23287</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1143; 10569</t>
+          <t>1029; 10569</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14708; 30116</t>
+          <t>16356; 32512</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10234</t>
+          <t>10909</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13872</t>
+          <t>15657</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24106</t>
+          <t>26566</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8299; 23781</t>
+          <t>8969; 23884</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6665; 25581</t>
+          <t>7315; 24634</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1138; 10140</t>
+          <t>934; 9789</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2467; 20731</t>
+          <t>5708; 19369</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5594; 20476</t>
+          <t>5454; 19082</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5089; 20542</t>
+          <t>5078; 19768</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2105; 13561</t>
+          <t>2145; 14513</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8733; 23027</t>
+          <t>9683; 25934</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17197; 38826</t>
+          <t>16890; 39046</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14894; 37562</t>
+          <t>15497; 37237</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5224; 19704</t>
+          <t>5149; 19975</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9448; 38526</t>
+          <t>18098; 39340</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26860</t>
+          <t>29111</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>24845</t>
+          <t>29323</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>51704</t>
+          <t>58434</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41183; 68589</t>
+          <t>41455; 69102</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17751; 38791</t>
+          <t>17953; 38896</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15152; 36664</t>
+          <t>15707; 35606</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18823; 37596</t>
+          <t>20094; 41120</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19928; 40759</t>
+          <t>18772; 39886</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14399; 32709</t>
+          <t>14457; 33553</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7847; 24661</t>
+          <t>8892; 24690</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11633; 36446</t>
+          <t>21644; 38635</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>66253; 101683</t>
+          <t>64762; 99774</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>37223; 64885</t>
+          <t>37177; 64295</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>27624; 54670</t>
+          <t>26532; 52556</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>35969; 66837</t>
+          <t>46704; 72449</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11147</t>
+          <t>12397</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>58530</t>
+          <t>59573</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>69677</t>
+          <t>71970</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5278; 16990</t>
+          <t>4871; 16279</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6575; 21733</t>
+          <t>6450; 21132</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7895; 22415</t>
+          <t>7959; 22375</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6770; 17933</t>
+          <t>7124; 20149</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>20154; 42195</t>
+          <t>18908; 41053</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>39911; 67497</t>
+          <t>39819; 66620</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31260; 58207</t>
+          <t>31122; 57508</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>43130; 79450</t>
+          <t>48770; 73449</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>28821; 53357</t>
+          <t>29012; 53165</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>50457; 82011</t>
+          <t>49207; 80926</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>43726; 73362</t>
+          <t>44057; 74677</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>54316; 90096</t>
+          <t>59522; 85225</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>56457</t>
+          <t>63216</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>56457</t>
+          <t>63216</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5621</t>
+          <t>0; 3998</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2987,42 +2987,42 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>66099; 102211</t>
+          <t>66739; 102540</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>88847; 130161</t>
+          <t>88357; 130218</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>46159; 78478</t>
+          <t>45552; 77170</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>47171; 69188</t>
+          <t>51208; 76875</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>67026; 101294</t>
+          <t>66058; 101639</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>90579; 131701</t>
+          <t>88577; 130334</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>44638; 76439</t>
+          <t>45183; 76967</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>45862; 69031</t>
+          <t>52341; 76321</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>58811</t>
+          <t>63805</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>182017</t>
+          <t>199043</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>240829</t>
+          <t>262848</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>77395; 117165</t>
+          <t>78458; 117945</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>54149; 91263</t>
+          <t>54908; 91894</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>33695; 59462</t>
+          <t>33403; 59666</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>43696; 73711</t>
+          <t>50416; 80871</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>149057; 198522</t>
+          <t>147818; 199668</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>178404; 233981</t>
+          <t>178253; 237844</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>109126; 155476</t>
+          <t>110166; 157081</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>144772; 207958</t>
+          <t>177650; 221210</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>235805; 300256</t>
+          <t>237447; 303552</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>244133; 311081</t>
+          <t>244023; 311940</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>151754; 208171</t>
+          <t>152224; 207539</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>201253; 270720</t>
+          <t>236404; 293616</t>
         </is>
       </c>
     </row>
